--- a/InsightsExtractor/data/hbfa_metrics.xlsx
+++ b/InsightsExtractor/data/hbfa_metrics.xlsx
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>53</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>37.74</v>
+        <v>43.4</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>1</v>
@@ -894,14 +894,14 @@
         <v>11.11</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>no-output</t>
+          <t>no-output,unknown</t>
         </is>
       </c>
     </row>
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>511</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>22.7</v>
+        <v>26.03</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>4</v>
@@ -983,13 +983,13 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="D11" s="17" t="n">
         <v>1511</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>7.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F11" s="17" t="n">
         <v>4</v>
@@ -1160,30 +1160,34 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1068</v>
+        <v>1191</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>1315</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>81.22</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>56</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>76.79000000000001</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>no-output</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1215,7 +1219,7 @@
         <v>5.71</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>1</v>
@@ -1238,22 +1242,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>109</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>58.72</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>8</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0</v>
@@ -1275,22 +1279,22 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>109</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0</v>
+        <v>48.62</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>8</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="I19" s="8" t="n">
         <v>0</v>
@@ -1598,22 +1602,22 @@
         </is>
       </c>
       <c r="D6" s="21" t="n">
-        <v>1086</v>
+        <v>1209</v>
       </c>
       <c r="E6" s="21" t="n">
         <v>1315</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>82.59</v>
+        <v>91.94</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>56</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>76.79000000000001</v>
+        <v>83.93000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1697,22 +1701,22 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>109</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0</v>
+        <v>58.72</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -1730,13 +1734,13 @@
         </is>
       </c>
       <c r="D10" s="21" t="n">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>511</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>36.4</v>
+        <v>39.73</v>
       </c>
       <c r="G10" s="21" t="n">
         <v>6</v>
@@ -1763,13 +1767,13 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>53</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>37.74</v>
+        <v>43.4</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>1</v>
